--- a/docs/위즈퍼링_카피라이팅_시트_v2_반영.xlsx
+++ b/docs/위즈퍼링_카피라이팅_시트_v2_반영.xlsx
@@ -1600,15 +1600,19 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>오늘 모든 참여를 완료하면 보너스 1,000원을 드려요</t>
+          <t>오늘 모든 참여를 완료하면 보너스 800원을 드려요</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>일일 완료 보너스 1,000 → 800원 (보상 표 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">

--- a/docs/위즈퍼링_카피라이팅_시트_v2_반영.xlsx
+++ b/docs/위즈퍼링_카피라이팅_시트_v2_반영.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>계정을 생성해 주세요</t>
+          <t>위즈퍼링에 로그인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>제목 변경</t>
+          <t>계정 생성 폼 → Google 로그인</t>
         </is>
       </c>
     </row>
@@ -486,74 +486,78 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WIZPR 서비스를 이용하기 위해 아래 정보를 입력해 주세요.</t>
+          <t>연구 담당자가 등록한 Google 계정으로 로그인해 주세요</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>문구수정</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>제목 셀에 붙어있던 안내문 분리</t>
+          <t>안내문 변경</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>onb_account_email</t>
+          <t>onb_login_google</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>이메일</t>
+          <t>Google로 계속하기</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>유일한 로그인 수단</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>onb_account_email_ph</t>
+          <t>onb_login_note</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>이메일을 입력해 주세요</t>
+          <t>휴대폰 인증 없이 Google 계정으로만 로그인해요. 성별·연락처 등 기본 정보는 연구 담당자가 등록해요.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>라벨 셀에 붙어있던 입력 플레이스홀더 분리</t>
+          <t>로그인 정책 안내</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>onb_account_pw</t>
+          <t>onb_login_signed</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>비밀번호</t>
+          <t>로그인됐어요</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -561,34 +565,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>onb_account_pw_ph</t>
+          <t>onb_login_issued_id</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>비밀번호를 입력해 주세요</t>
+          <t>발급된 연구 ID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>플레이스홀더 분리</t>
+          <t>이메일 기준 관리자 발급</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>onb_account_pwnotice</t>
+          <t>onb_login_info</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>영문, 숫자, 특수문자 포함 8자 이상</t>
+          <t>관리자가 등록한 기본 정보</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,26 +600,22 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>비밀번호 조건 안내</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>onb_account_pwagain</t>
+          <t>common_next</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>비밀번호 확인</t>
+          <t>다음</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -623,34 +623,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>onb_account_pwagain_ph</t>
+          <t>onb_pairing_title</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>비밀번호를 다시 입력해 주세요</t>
+          <t>WIZPR RING을 연결해 주세요</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>문구수정</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>플레이스홀더 분리</t>
+          <t>제목 변경, 끝 개행 제거</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>onb_account_phone</t>
+          <t>onb_pairing_sub</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>휴대폰 번호</t>
+          <t>반지를 손가락에 착용한 상태로 진행해 주세요</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -663,78 +663,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>onb_account_phone_ph</t>
+          <t>onb_pairing_scanning</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>'-' 없이 휴대폰 번호를 입력해 주세요</t>
+          <t>연결 가능한 WIZPR RING을 검색 중입니다.
+잠시만 기다려 주세요.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>문구수정</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>플레이스홀더 분리</t>
+          <t>안내문 변경 (2줄 의도된 개행)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>onb_account_verify</t>
+          <t>onb_pairing_connect</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>인증하기</t>
+          <t>연결</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>문구수정</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>버튼 라벨</t>
+          <t>'연결하기' → '연결'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>onb_account_verify_ph</t>
+          <t>onb_pairing_rescan</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>인증번호 6자리를 입력해 주세요</t>
+          <t>다시 검색</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>인증번호 입력 플레이스홀더 (버튼과 분리)</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>onb_account_verified</t>
+          <t>onb_pairing_help</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>인증됨</t>
+          <t>페어링에 문제가 있나요?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -747,74 +744,71 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>onb_account_birth</t>
+          <t>onb_perm_title</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>연구에 필요한 권한을
+허용해 주세요</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>출생연도 → 연령</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>onb_account_birth_ph</t>
+          <t>onb_perm_sub</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>연령을 선택해 주세요</t>
+          <t>권한이 꺼져 있는 동안의 기록은 다시 수집할 수 없어요</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>플레이스홀더 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>onb_account_sex</t>
+          <t>onb_perm_noti</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>분리</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>'알림 — 설명' em-dash 라벨/설명 분리</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>onb_account_sex_female</t>
+          <t>onb_perm_noti_desc</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>여성</t>
+          <t>설문 시간을 알려드려요</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -822,21 +816,17 @@
           <t>분리</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>'남성/여성' 옵션 분리</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>onb_account_sex_male</t>
+          <t>onb_perm_loc</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>남성</t>
+          <t>위치</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -846,24 +836,24 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>'남성/여성' 옵션 분리</t>
+          <t>em-dash 분리</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>common_next</t>
+          <t>onb_perm_loc_desc</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>외출 반경과 이동 거리를 계산해요</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -871,39 +861,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>onb_pairing_title</t>
+          <t>onb_perm_activity</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>WIZPR RING을 연결해 주세요</t>
+          <t>신체활동</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>문구수정</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>제목 변경, 끝 개행 제거</t>
+          <t>em-dash 분리</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>onb_pairing_sub</t>
+          <t>onb_perm_activity_desc</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>반지를 손가락에 착용한 상태로 진행해 주세요</t>
+          <t>걸음 수와 활동 시간을 수집해요</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -911,80 +901,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>onb_pairing_scanning</t>
+          <t>onb_perm_bt</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>연결 가능한 WIZPR RING을 검색 중입니다.
-잠시만 기다려 주세요.</t>
+          <t>Bluetooth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>문구수정</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>안내문 변경 (2줄 의도된 개행)</t>
+          <t>em-dash 분리</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>onb_pairing_connect</t>
+          <t>onb_perm_bt_desc</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>연결</t>
+          <t>반지와 연결을 유지해요</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>'연결하기' → '연결'</t>
-        </is>
-      </c>
+          <t>분리</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>onb_pairing_rescan</t>
+          <t>onb_perm_battery</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>다시 검색</t>
+          <t>배터리 사용 제한 해제</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>분리</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>em-dash 분리</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>onb_pairing_help</t>
+          <t>onb_perm_battery_desc</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>페어링에 문제가 있나요?</t>
+          <t>백그라운드 수집이 끊기지 않아요</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>분리</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -992,13 +981,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>onb_perm_title</t>
+          <t>onb_perm_go_settings</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>연구에 필요한 권한을
-허용해 주세요</t>
+          <t>설정하러 가기</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1011,12 +999,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>onb_perm_sub</t>
+          <t>onb_perm_allowed</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>권한이 꺼져 있는 동안의 기록은 다시 수집할 수 없어요</t>
+          <t>허용됨</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1029,39 +1017,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>onb_perm_noti</t>
+          <t>onb_perm_privacy</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>위치 좌표나 통화 내용 원문은 서버로 보내지 않아요. 기기 안에서 계산한 값만 전송돼요.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>'알림 — 설명' em-dash 라벨/설명 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>onb_perm_noti_desc</t>
+          <t>onb_time_title</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>설문 시간을 알려드려요</t>
+          <t>첫 설문 시간을
+골라 주세요</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -1069,39 +1054,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>onb_perm_loc</t>
+          <t>onb_time_sub</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>하루 4번, 4시간 간격으로 진행돼요. 일과를 시작한 뒤의 시간을 고르면 참여하기 좋아요.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>em-dash 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>onb_perm_loc_desc</t>
+          <t>onb_time_manual</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>외출 반경과 이동 거리를 계산해요</t>
+          <t>직접 선택</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -1109,39 +1090,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>onb_perm_activity</t>
+          <t>onb_time_auto</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>신체활동</t>
+          <t>자동 설정</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>em-dash 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>onb_perm_activity_desc</t>
+          <t>onb_time_lock</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>걸음 수와 활동 시간을 수집해요</t>
+          <t>연구 시작 후에는 시간을 바꿀 수 없어요. 각 회차는 알림 후 60분 동안 참여할 수 있어요.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1149,39 +1126,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>onb_perm_bt</t>
+          <t>onb_time_confirm_title</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Bluetooth</t>
+          <t>이 시간으로 확정할까요?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>em-dash 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>onb_perm_bt_desc</t>
+          <t>onb_time_confirm_body</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>반지와 연결을 유지해요</t>
+          <t>설정한 시간으로 설문 알림이 발송돼요.
+연구가 시작되면 직접 변경할 수 없어요.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -1189,39 +1163,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>onb_perm_battery</t>
+          <t>onb_time_confirm_yes</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>배터리 사용 제한 해제</t>
+          <t>확정하기</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>분리</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>em-dash 분리</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>onb_perm_battery_desc</t>
+          <t>onb_time_confirm_no</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>백그라운드 수집이 끊기지 않아요</t>
+          <t>다시 고르기</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>분리</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -1229,12 +1199,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>onb_perm_go_settings</t>
+          <t>onb_ready_title</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>설정하러 가기</t>
+          <t>준비가 끝났어요</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1247,12 +1217,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>onb_perm_allowed</t>
+          <t>onb_ready_first_ema</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>허용됨</t>
+          <t>첫 설문 예정</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1265,12 +1235,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>onb_perm_privacy</t>
+          <t>onb_ready_start</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>위치 좌표나 통화 내용 원문은 서버로 보내지 않아요. 기기 안에서 계산한 값만 전송돼요.</t>
+          <t>앱 시작하기</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1283,13 +1253,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>onb_time_title</t>
+          <t>home_greeting</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>첫 설문 시간을
-골라 주세요</t>
+          <t>안녕하세요, {id}님</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1297,17 +1266,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>{id}=연구 ID</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>onb_time_sub</t>
+          <t>home_greeting_sub</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>하루 4번, 4시간 간격으로 진행돼요. 일과를 시작한 뒤의 시간을 고르면 참여하기 좋아요.</t>
+          <t>오늘도 소중한 참여 부탁드려요</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1320,12 +1293,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>onb_time_manual</t>
+          <t>home_today_earned</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>직접 선택</t>
+          <t>오늘 적립액</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1338,12 +1311,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>onb_time_auto</t>
+          <t>home_total</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>자동 설정</t>
+          <t>총 누적액</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1356,12 +1329,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>onb_time_lock</t>
+          <t>home_reset_note</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>연구 시작 후에는 시간을 바꿀 수 없어요. 각 회차는 알림 후 60분 동안 참여할 수 있어요.</t>
+          <t>매일 자정에 총 누적액으로 옮겨져요</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1374,31 +1347,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>onb_time_confirm_title</t>
+          <t>home_bonus_banner</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>이 시간으로 확정할까요?</t>
+          <t>오늘 모든 참여를 완료하면 보너스 800원을 드려요</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>일일 완료 보너스 1,000 → 800원 (보상 표 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>onb_time_confirm_body</t>
+          <t>home_today_survey</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>설정한 시간으로 설문 알림이 발송돼요.
-연구가 시작되면 직접 변경할 수 없어요.</t>
+          <t>오늘의 설문</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1411,30 +1387,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>onb_time_confirm_yes</t>
+          <t>home_survey_sub</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>확정하기</t>
+          <t>하루 4번, 각 회차 1시간 이내에 참여할 수 있어요</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>60분 → 1시간</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>onb_time_confirm_no</t>
+          <t>home_join</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>다시 고르기</t>
+          <t>참여하기</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1447,12 +1427,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>onb_ready_title</t>
+          <t>home_done</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>준비가 끝났어요</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1465,12 +1445,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>onb_ready_first_ema</t>
+          <t>home_opens_at</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>첫 설문 예정</t>
+          <t>{n}시에 열려요</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1478,17 +1458,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>{n}=회차 시각(시)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>onb_ready_start</t>
+          <t>home_today_voice</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>앱 시작하기</t>
+          <t>오늘의 음성 과제</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1501,12 +1485,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>home_greeting</t>
+          <t>home_progress</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>안녕하세요, {id}님</t>
+          <t>오늘의 진행</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1514,21 +1498,17 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>{id}=연구 ID</t>
-        </is>
-      </c>
+      <c r="D55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>home_greeting_sub</t>
+          <t>home_calendar</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>오늘도 소중한 참여 부탁드려요</t>
+          <t>참여 현황</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1541,53 +1521,61 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>home_today_earned</t>
+          <t>ema_title</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>오늘 적립액</t>
+          <t>설문 응답</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>'{t} 자기보고 설문' → '설문 응답' ({t} 제거)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>home_total</t>
+          <t>ema_loneliness_instruction</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>총 누적액</t>
+          <t>지난 설문 시점으로부터 현재까지 다음의 문제에 해당하는 정도를 선택해 주세요.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>외로움 척도 안내</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>home_reset_note</t>
+          <t>ema_loneliness_ask_1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>매일 자정에 총 누적액으로 옮겨져요</t>
+          <t>나는 나와 같이 있어 줄 사람이 부족하다.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -1595,39 +1583,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>home_bonus_banner</t>
+          <t>ema_loneliness_ask_2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>오늘 모든 참여를 완료하면 보너스 800원을 드려요</t>
+          <t>나는 혼자 남겨진 것 같다고 느껴진다.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>일일 완료 보너스 1,000 → 800원 (보상 표 기준)</t>
-        </is>
-      </c>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>home_today_survey</t>
+          <t>ema_loneliness_ask_3</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>오늘의 설문</t>
+          <t>나는 사람들 사이에서 고립되어 있다고 느껴진다.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -1635,39 +1619,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>home_survey_sub</t>
+          <t>ema_loneliness_scale_1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>하루 4번, 각 회차 1시간 이내에 참여할 수 있어요</t>
+          <t>전혀 그렇지 않다</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>60분 → 1시간</t>
-        </is>
-      </c>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>home_join</t>
+          <t>ema_loneliness_scale_2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>참여하기</t>
+          <t>가끔 그렇다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -1675,17 +1655,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>home_done</t>
+          <t>ema_loneliness_scale_3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>자주 그렇다</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -1693,39 +1673,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>home_opens_at</t>
+          <t>ema_phq_instruction</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>{n}시에 열려요</t>
+          <t>지난 설문 시점으로부터 현재까지 다음의 문제에 해당하는 정도를 1~5까지 선택해 주세요.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>{n}=회차 시각(시)</t>
+          <t>PHQ-9 안내</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>home_today_voice</t>
+          <t>ema_phq_ask_1</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>오늘의 음성 과제</t>
+          <t>기분이 가라앉거나, 우울하거나, 희망이 없다고 느낌</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -1733,17 +1713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>home_progress</t>
+          <t>ema_phq_ask_2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>오늘의 진행</t>
+          <t>평소 하던 일에 대한 흥미가 없어지거나 즐거움을 느끼지 못함</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -1751,17 +1731,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>home_calendar</t>
+          <t>ema_phq_ask_3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>참여 현황</t>
+          <t>잠들기가 어렵거나 자주 깸, 혹은 너무 많이 잤음</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -1769,34 +1749,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ema_title</t>
+          <t>ema_phq_ask_4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>설문 응답</t>
+          <t>평소보다 식욕이 줄었음, 혹은 평소보다 많이 먹음</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>'{t} 자기보고 설문' → '설문 응답' ({t} 제거)</t>
-        </is>
-      </c>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ema_loneliness_instruction</t>
+          <t>ema_phq_ask_5</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>지난 설문 시점으로부터 현재까지 다음의 문제에 해당하는 정도를 선택해 주세요.</t>
+          <t>다른 사람들이 눈치챌 정도로 평소보다 말과 행동이 느려짐, 혹은 너무 안절부절못해서 가만히 앉아 있을 수 없음</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1804,21 +1780,17 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>외로움 척도 안내</t>
-        </is>
-      </c>
+      <c r="D70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ema_loneliness_ask_1</t>
+          <t>ema_phq_ask_6</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>나는 나와 같이 있어 줄 사람이 부족하다.</t>
+          <t>피곤하거나 기운이 없음</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1831,12 +1803,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ema_loneliness_ask_2</t>
+          <t>ema_phq_ask_7</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>나는 혼자 남겨진 것 같다고 느껴진다.</t>
+          <t>내가 잘못했거나 실패했다는 생각이 듦, 혹은 자신과 가족을 실망시켰다고 생각함</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1849,12 +1821,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ema_loneliness_ask_3</t>
+          <t>ema_phq_ask_8</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>나는 사람들 사이에서 고립되어 있다고 느껴진다.</t>
+          <t>신문을 읽거나 TV를 보는 것과 같은 일상적인 일에도 집중할 수 없었음</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1867,12 +1839,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ema_loneliness_scale_1</t>
+          <t>ema_phq_ask_9</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>전혀 그렇지 않다</t>
+          <t>차라리 죽는 것이 더 낫겠다고 생각함, 혹은 자해할 생각을 함</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1885,12 +1857,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ema_loneliness_scale_2</t>
+          <t>ema_phq_scale_1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>가끔 그렇다</t>
+          <t>전혀 해당되지 않음</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1898,17 +1870,21 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>척도 최저 (1)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ema_loneliness_scale_3</t>
+          <t>ema_phq_scale_5</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>자주 그렇다</t>
+          <t>매우 해당함</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1916,12 +1892,16 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>척도 최고 (5)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ema_phq_instruction</t>
+          <t>ema_gad_instruction</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1936,19 +1916,19 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>PHQ-9 안내</t>
+          <t>GAD-7 안내</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ema_phq_ask_1</t>
+          <t>ema_gad_ask_1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>기분이 가라앉거나, 우울하거나, 희망이 없다고 느낌</t>
+          <t>초조하거나 불안하거나 조마조마하게 느낀다.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1961,12 +1941,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ema_phq_ask_2</t>
+          <t>ema_gad_ask_2</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>평소 하던 일에 대한 흥미가 없어지거나 즐거움을 느끼지 못함</t>
+          <t>걱정하는 것을 멈추거나 조절할 수가 없다.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1979,12 +1959,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ema_phq_ask_3</t>
+          <t>ema_gad_ask_3</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>잠들기가 어렵거나 자주 깸, 혹은 너무 많이 잤음</t>
+          <t>여러 가지 것들에 대해 걱정을 너무 많이 한다.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1997,12 +1977,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ema_phq_ask_4</t>
+          <t>ema_gad_ask_4</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>평소보다 식욕이 줄었음, 혹은 평소보다 많이 먹음</t>
+          <t>편하게 있기가 어렵다.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2015,12 +1995,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ema_phq_ask_5</t>
+          <t>ema_gad_ask_5</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>다른 사람들이 눈치챌 정도로 평소보다 말과 행동이 느려짐, 혹은 너무 안절부절못해서 가만히 앉아 있을 수 없음</t>
+          <t>너무 안절부절못해서 가만히 있기가 힘들다.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2033,12 +2013,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ema_phq_ask_6</t>
+          <t>ema_gad_ask_6</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>피곤하거나 기운이 없음</t>
+          <t>쉽게 짜증이 나거나 쉽게 성을 내게 된다.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2051,12 +2031,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ema_phq_ask_7</t>
+          <t>ema_gad_ask_7</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>내가 잘못했거나 실패했다는 생각이 듦, 혹은 자신과 가족을 실망시켰다고 생각함</t>
+          <t>마치 끔찍한 일이 생길 것처럼 두렵게 느껴진다.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2069,48 +2049,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ema_phq_ask_8</t>
+          <t>ema_gad_scale_1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>신문을 읽거나 TV를 보는 것과 같은 일상적인 일에도 집중할 수 없었음</t>
+          <t>전혀 해당되지 않음</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
+          <t>변수명수정</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>'ema_gad_1' → 'ema_gad_scale_1'</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ema_phq_ask_9</t>
+          <t>ema_gad_scale_5</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>차라리 죽는 것이 더 낫겠다고 생각함, 혹은 자해할 생각을 함</t>
+          <t>매우 해당함</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>변수명수정</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>'ema_gad_5' → 'ema_gad_scale_5'</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ema_phq_scale_1</t>
+          <t>ema_esm_instruction</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>전혀 해당되지 않음</t>
+          <t>알림이 울리기 직전의 상태를 떠올리고 답해 주세요.
+각 문항에 대해 1(전혀 아니다) ~ 7(매우 그렇다) 중 해당하는 정도를 선택해 주세요.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2120,19 +2109,19 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>척도 최저 (1)</t>
+          <t>ESM 안내</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ema_phq_scale_5</t>
+          <t>ema_esm_ask_1</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>매우 해당함</t>
+          <t>내 생각을 말로 표현하기 어렵다.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2140,21 +2129,17 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>척도 최고 (5)</t>
-        </is>
-      </c>
+      <c r="D88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ema_gad_instruction</t>
+          <t>ema_esm_ask_2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>지난 설문 시점으로부터 현재까지 다음의 문제에 해당하는 정도를 1~5까지 선택해 주세요.</t>
+          <t>내 생각이 다른 사람의 영향을 받는다.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2162,21 +2147,17 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>GAD-7 안내</t>
-        </is>
-      </c>
+      <c r="D89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ema_gad_ask_1</t>
+          <t>ema_esm_ask_3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>초조하거나 불안하거나 조마조마하게 느낀다.</t>
+          <t>어떤 생각을 머릿속에서 떨쳐낼 수 없다.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2189,12 +2170,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ema_gad_ask_2</t>
+          <t>ema_esm_ask_4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>걱정하는 것을 멈추거나 조절할 수가 없다.</t>
+          <t>내가 현실이 아닌 것처럼 느껴진다.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2207,12 +2188,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ema_gad_ask_3</t>
+          <t>ema_esm_ask_5</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>여러 가지 것들에 대해 걱정을 너무 많이 한다.</t>
+          <t>누군가 나를 해치려 한다는 의심이 든다.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2225,12 +2206,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ema_gad_ask_4</t>
+          <t>ema_esm_ask_6</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>편하게 있기가 어렵다.</t>
+          <t>실제로는 없는 소리가 들린다.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2243,12 +2224,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ema_gad_ask_5</t>
+          <t>ema_esm_ask_7</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>너무 안절부절못해서 가만히 있기가 힘들다.</t>
+          <t>실제로는 없는 것이 보인다.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2261,12 +2242,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ema_gad_ask_6</t>
+          <t>ema_esm_ask_8</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>쉽게 짜증이 나거나 쉽게 성을 내게 된다.</t>
+          <t>내가 통제력을 잃어가고 있는 것 같다.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2279,12 +2260,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ema_gad_ask_7</t>
+          <t>ema_esm_scale_1</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>마치 끔찍한 일이 생길 것처럼 두렵게 느껴진다.</t>
+          <t>전혀 아니다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2292,89 +2273,85 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>척도 최저 (1)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ema_gad_scale_1</t>
+          <t>ema_esm_scale_7</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>전혀 해당되지 않음</t>
+          <t>매우 그렇다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>변수명수정</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>'ema_gad_1' → 'ema_gad_scale_1'</t>
+          <t>척도 최고 (7)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ema_gad_scale_5</t>
+          <t>ema_next_blocked</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>매우 해당함</t>
+          <t>모든 문항에 답하면 넘어갈 수 있어요</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>변수명수정</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>'ema_gad_5' → 'ema_gad_scale_5'</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ema_esm_instruction</t>
+          <t>ema_exit_title</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>알림이 울리기 직전의 상태를 떠올리고 답해 주세요.
-각 문항에 대해 1(전혀 아니다) ~ 7(매우 그렇다) 중 해당하는 정도를 선택해 주세요.</t>
+          <t>설문을 그만할까요?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>ESM 안내</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ema_esm_ask_1</t>
+          <t>ema_exit_body</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>내 생각을 말로 표현하기 어렵다.</t>
+          <t>지금 그만두면 응답이 저장되지 않고
+이번 회차 보상 250원도 받을 수 없어요.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -2382,17 +2359,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ema_esm_ask_2</t>
+          <t>ema_exit_continue</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>내 생각이 다른 사람의 영향을 받는다.</t>
+          <t>계속 응답하기</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -2400,17 +2377,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ema_esm_ask_3</t>
+          <t>ema_exit_quit</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>어떤 생각을 머릿속에서 떨쳐낼 수 없다.</t>
+          <t>그만하기</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -2418,17 +2395,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ema_esm_ask_4</t>
+          <t>ema_done_title</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>내가 현실이 아닌 것처럼 느껴진다.</t>
+          <t>250원이 적립됐어요</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -2436,53 +2413,61 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ema_esm_ask_5</t>
+          <t>ema_done_sub</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>누군가 나를 해치려 한다는 의심이 든다.</t>
+          <t>오늘 {n}번째 설문까지 완료했어요</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>{n}=오늘 완료 회차 수</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ema_esm_ask_6</t>
+          <t>ema_done_next</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>실제로는 없는 소리가 들린다.</t>
+          <t>다음 과제는 {t}시에 열려요. 알림으로 알려드릴게요.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>'설문'→'과제', {t} 뒤 '시' 추가 ({t}=시각 숫자)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ema_esm_ask_7</t>
+          <t>common_home</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>실제로는 없는 것이 보인다.</t>
+          <t>홈으로</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -2490,17 +2475,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ema_esm_ask_8</t>
+          <t>voice_title</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>내가 통제력을 잃어가고 있는 것 같다.</t>
+          <t>음성 대화 과제</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -2508,56 +2493,48 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ema_esm_scale_1</t>
+          <t>voice_topic_label</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>전혀 아니다</t>
+          <t>오늘의 대화 주제</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>척도 최저 (1)</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ema_esm_scale_7</t>
+          <t>voice_topic_sub</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>매우 그렇다</t>
+          <t>답변에 따라 이어지는 질문을 드려요</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>척도 최고 (7)</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ema_next_blocked</t>
+          <t>voice_guide_quiet</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>모든 문항에 답하면 넘어갈 수 있어요</t>
+          <t>조용한 곳에서 편하게 이야기해 주세요</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2570,12 +2547,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ema_exit_title</t>
+          <t>voice_guide_time</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>설문을 그만할까요?</t>
+          <t>최소 20초, 최대 2분 동안 진행돼요</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2588,31 +2565,34 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ema_exit_body</t>
+          <t>voice_guide_free</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>지금 그만두면 응답이 저장되지 않고
-이번 회차 보상 250원도 받을 수 없어요.</t>
+          <t>정답은 없어요. 떠오르는 대로 말해 주세요.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>마침표 추가</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ema_exit_continue</t>
+          <t>voice_start</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>계속 응답하기</t>
+          <t>대화 시작하기</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2625,30 +2605,34 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ema_exit_quit</t>
+          <t>voice_start_reward</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>그만하기</t>
+          <t>완료하면 700원이 적립돼요</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>500원 → 700원</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ema_done_title</t>
+          <t>voice_ring_connected</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>250원이 적립됐어요</t>
+          <t>WIZPR RING 연결됨</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2661,12 +2645,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ema_done_sub</t>
+          <t>voice_ring_required</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>오늘 {n}번째 설문까지 완료했어요</t>
+          <t>반지를 연결해야 시작할 수 있어요</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2674,61 +2658,57 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>{n}=오늘 완료 회차 수</t>
-        </is>
-      </c>
+      <c r="D116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ema_done_next</t>
+          <t>voice_followup_note</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>다음 과제는 {t}시에 열려요. 알림으로 알려드릴게요.</t>
+          <t>이어지는 질문 · 음성으로도 들려드려요</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>'설문'→'과제', {t} 뒤 '시' 추가 ({t}=시각 숫자)</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>common_home</t>
+          <t>voice_min_ok</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>홈으로</t>
+          <t>최소 시간을 채웠어요. 지금 마쳐도 돼요</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>em-dash 제거</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>voice_title</t>
+          <t>voice_pause_hint</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>음성 대화 과제</t>
+          <t>말이 3초 이상 끊기면 안내를 드려요</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2741,12 +2721,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>voice_topic_label</t>
+          <t>voice_finish</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>오늘의 대화 주제</t>
+          <t>녹음 완료</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2759,30 +2739,34 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>voice_topic_sub</t>
+          <t>voice_done_title</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>답변에 따라 이어지는 질문을 드려요</t>
+          <t>700원이 적립됐어요</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>500원 → 700원</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>voice_guide_quiet</t>
+          <t>voice_done_sub</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>조용한 곳에서 편하게 이야기해 주세요</t>
+          <t>오늘 과제를 모두 마쳤어요</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2795,12 +2779,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>voice_guide_time</t>
+          <t>voice_bonus_title</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>최소 20초, 최대 2분 동안 진행돼요</t>
+          <t>모든 참여 완료 보너스</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2813,34 +2797,30 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>voice_guide_free</t>
+          <t>voice_bonus_sub</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>정답은 없어요. 떠오르는 대로 말해 주세요.</t>
+          <t>설문 4회 + 대화 1회</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>마침표 추가</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>voice_start</t>
+          <t>voice_next_day</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>대화 시작하기</t>
+          <t>다음 참여일</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2853,34 +2833,30 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>voice_start_reward</t>
+          <t>device_title</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>완료하면 700원이 적립돼요</t>
+          <t>기기 연결</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>500원 → 700원</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>voice_ring_connected</t>
+          <t>device_connected</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>WIZPR RING 연결됨</t>
+          <t>연결됨 · 방금 동기화</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2893,12 +2869,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>voice_ring_required</t>
+          <t>device_battery</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>반지를 연결해야 시작할 수 있어요</t>
+          <t>반지 배터리</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2911,12 +2887,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>voice_followup_note</t>
+          <t>device_last_sync</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>이어지는 질문 · 음성으로도 들려드려요</t>
+          <t>마지막 데이터 전송</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2929,34 +2905,30 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>voice_min_ok</t>
+          <t>device_auto_reconnect</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>최소 시간을 채웠어요. 지금 마쳐도 돼요</t>
+          <t>연결이 끊기면 자동으로 다시 연결을 시도해요. 계속 실패하면 알림으로 알려드려요.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>em-dash 제거</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>voice_pause_hint</t>
+          <t>device_reconnect</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>말이 3초 이상 끊기면 안내를 드려요</t>
+          <t>다시 연결하기</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2969,12 +2941,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>voice_finish</t>
+          <t>settings_title</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>녹음 완료</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2987,34 +2959,30 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>voice_done_title</t>
+          <t>settings_doc</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>700원이 적립됐어요</t>
+          <t>연구 설명문 보기</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>500원 → 700원</t>
-        </is>
-      </c>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>voice_done_sub</t>
+          <t>settings_perm</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>오늘 과제를 모두 마쳤어요</t>
+          <t>권한 상태 확인</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3027,12 +2995,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>voice_bonus_title</t>
+          <t>settings_perm_alert</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>모든 참여 완료 보너스</t>
+          <t>{n}개 확인 필요</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3040,17 +3008,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>{n}=미허용 권한 수</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>voice_bonus_sub</t>
+          <t>settings_noti</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>설문 4회 + 대화 1회</t>
+          <t>알림 설정</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3063,12 +3035,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>voice_next_day</t>
+          <t>settings_ema_time</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>다음 참여일</t>
+          <t>설문 시간</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3081,12 +3053,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>device_title</t>
+          <t>settings_ema_locked</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>기기 연결</t>
+          <t>{t} 시작 · 변경 불가</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3094,17 +3066,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>{t}=1회차 시각</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>device_connected</t>
+          <t>settings_contact</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>연결됨 · 방금 동기화</t>
+          <t>연구팀에 문의하기</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3117,12 +3093,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>device_battery</t>
+          <t>settings_withdraw</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>반지 배터리</t>
+          <t>연구 참여 철회</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3135,12 +3111,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>device_last_sync</t>
+          <t>settings_withdraw_note</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>마지막 데이터 전송</t>
+          <t>참여 철회 시 이후 수집이 즉시 중단돼요. 자세한 내용은 연구 설명문을 확인해 주세요.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3153,12 +3129,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>device_auto_reconnect</t>
+          <t>push_session_open</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>연결이 끊기면 자동으로 다시 연결을 시도해요. 계속 실패하면 알림으로 알려드려요.</t>
+          <t>{t} 설문에 참여할 수 있어요. 60분 동안 열려 있어요.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3166,35 +3142,43 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>{t}=회차 시각</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>device_reconnect</t>
+          <t>push_day_start</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>다시 연결하기</t>
+          <t>오늘은 설문 및 대화과제 참여가 가능한 날입니다. 오늘 4번의 설문과 1번의 대화과제를 모두 참여하시면 2,500원이 지급됩니다.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
+          <t>문구수정</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>1,500원 → 2,500원</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>settings_title</t>
+          <t>push_ema_low</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>오늘은 설문 및 대화과제 참여가 가능한 날입니다. 지난 8회의 설문 중 총 {n}회 참여하셨습니다. 원활한 연구 진행을 위해 성실히 참여해주시면 감사하겠습니다!</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3202,17 +3186,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>{n}=참여 횟수</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>settings_doc</t>
+          <t>push_sensor_low</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>연구 설명문 보기</t>
+          <t>어제의 센서 수집이 원활하지 않았습니다. 다음 안내에 따라 조치하신 후 설문에 참여해 주세요.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3225,12 +3213,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>settings_perm</t>
+          <t>push_voice_low</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>권한 상태 확인</t>
+          <t>최근 대화형 과제에 {n}회 연속 참여하지 않으셨습니다. 잊지 말고 참여해 주세요!</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3238,17 +3226,21 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>{n}=연속 미응답 횟수</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>settings_perm_alert</t>
+          <t>push_reminder</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>{n}개 확인 필요</t>
+          <t>이번 회차 EMA 응답 가능 시간이 30분밖에 남지 않았습니다. 응답 시간이 지나면 이번 회차는 참여가 어려우니, 잊지 마시고 꼭 확인 부탁드립니다.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3256,247 +3248,7 @@
           <t>유지</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>{n}=미허용 권한 수</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>settings_noti</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>알림 설정</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>settings_ema_time</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>설문 시간</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>settings_ema_locked</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>{t} 시작 · 변경 불가</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>{t}=1회차 시각</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>settings_contact</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>연구팀에 문의하기</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>settings_withdraw</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>연구 참여 철회</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>settings_withdraw_note</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>참여 철회 시 이후 수집이 즉시 중단돼요. 자세한 내용은 연구 설명문을 확인해 주세요.</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>push_session_open</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>{t} 설문에 참여할 수 있어요. 60분 동안 열려 있어요.</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>{t}=회차 시각</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>push_day_start</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>오늘은 설문 및 대화과제 참여가 가능한 날입니다. 오늘 4번의 설문과 1번의 대화과제를 모두 참여하시면 2,500원이 지급됩니다.</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>문구수정</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>1,500원 → 2,500원</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>push_ema_low</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>오늘은 설문 및 대화과제 참여가 가능한 날입니다. 지난 8회의 설문 중 총 {n}회 참여하셨습니다. 원활한 연구 진행을 위해 성실히 참여해주시면 감사하겠습니다!</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>{n}=참여 횟수</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>push_sensor_low</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>어제의 센서 수집이 원활하지 않았습니다. 다음 안내에 따라 조치하신 후 설문에 참여해 주세요.</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>push_voice_low</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>최근 대화형 과제에 {n}회 연속 참여하지 않으셨습니다. 잊지 말고 참여해 주세요!</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>{n}=연속 미응답 횟수</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>push_reminder</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>이번 회차 EMA 응답 가능 시간이 30분밖에 남지 않았습니다. 응답 시간이 지나면 이번 회차는 참여가 어려우니, 잊지 마시고 꼭 확인 부탁드립니다.</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+      <c r="D147" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
